--- a/Hindi 24 sentences.xlsx
+++ b/Hindi 24 sentences.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\my pc\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba77bf8d4b5edec/Desktop/IIITH DOCUMENTS/prosody_questionnaire/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DEE3E5E-3129-4C22-AA4F-6F387D9FCA31}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="120">
   <si>
     <t>sample id</t>
   </si>
@@ -374,42 +374,6 @@
   </si>
   <si>
     <t>2288136.mp3</t>
-  </si>
-  <si>
-    <t>the children are using statistics to find out about the world, but after all, scientists also do experiments, and we wanted to see if children are doing experiments.</t>
-  </si>
-  <si>
-    <t>बच्चे सांख्यिकी का इस्तेमाल कर के दुनिया को जान समझ रहे हैं, मगर क्योंकि साइंसटिस्ट प्रयोग करते हैं, तो हम ये जानना चाहते थे कि क्या बच्चे भी प्रयोग करते हैं।</t>
-  </si>
-  <si>
-    <t>if</t>
-  </si>
-  <si>
-    <t>क्या</t>
-  </si>
-  <si>
-    <t>cplaWsiu7Yg_sentence_00305.m4a</t>
-  </si>
-  <si>
-    <t>So this study got me wondering: Can changing how you think about stress make you healthier?</t>
-  </si>
-  <si>
-    <t>इस अभ्यासने मै चकित हूँई| क्या हम अपनी तनाव की सोच बदलकर स्वास्थ पा सकते है?</t>
-  </si>
-  <si>
-    <t>can</t>
-  </si>
-  <si>
-    <t>RcGyVTAoXEU_sentence_01234.m4a</t>
-  </si>
-  <si>
-    <t>I don't know if Tom will tell the truth or not.</t>
-  </si>
-  <si>
-    <t>मैं नहीं जानता कि क्या टॉम सच बोलेगा या नहीं?</t>
-  </si>
-  <si>
-    <t>6431014.mp3</t>
   </si>
   <si>
     <t>they're</t>
@@ -755,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1145,7 +1109,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H15" t="s">
         <v>77</v>
@@ -1197,7 +1161,7 @@
         <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
         <v>77</v>
@@ -1334,75 +1298,6 @@
       </c>
       <c r="I22" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>305</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>1234</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>6431014</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="G25" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" t="s">
-        <v>121</v>
-      </c>
-      <c r="I25" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Hindi 24 sentences.xlsx
+++ b/Hindi 24 sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba77bf8d4b5edec/Desktop/IIITH DOCUMENTS/prosody_questionnaire/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DEE3E5E-3129-4C22-AA4F-6F387D9FCA31}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F03BCFB-37AF-48DB-9CD1-1CA3791C23E3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="141">
   <si>
     <t>sample id</t>
   </si>
@@ -380,6 +380,69 @@
   </si>
   <si>
     <t>That's</t>
+  </si>
+  <si>
+    <t>इस सबका मतलब यह है।</t>
+  </si>
+  <si>
+    <t>बस इतना मुझे कहना है । शुक्रिया ।</t>
+  </si>
+  <si>
+    <t>और यह एक बहुत अच्छा विचार है</t>
+  </si>
+  <si>
+    <t>सभी का कल्याण करना, यह तो समुदाय का काम है।</t>
+  </si>
+  <si>
+    <t>पर यह सब था​.</t>
+  </si>
+  <si>
+    <t>वो तो पूरा अंग्रेजी में है।"</t>
+  </si>
+  <si>
+    <t>इस समझ की शुरुआत कहाँ से करें?</t>
+  </si>
+  <si>
+    <t>हम बढ़िया कंप्यूटर बनाते हैं.</t>
+  </si>
+  <si>
+    <t>मैंने यह सोचा, क्या यह स्पष्ट नहीं है?</t>
+  </si>
+  <si>
+    <t>वास्तव में उनके कुछ विचार गलत थे.</t>
+  </si>
+  <si>
+    <t>मुझे जीव विज्ञान कभी पसंद नहीं था।</t>
+  </si>
+  <si>
+    <t>तुम्हारे पास जहाँ जाने की मर्ज़ी हो वहाँ जाने की आज़ादी है।</t>
+  </si>
+  <si>
+    <t>होसकता है आप उस पल की गर्मी मेँ अपना मन बदलेँ, लेकिन कम से कम आप इस तरह की सोच की अभ्यास कर चुके है|</t>
+  </si>
+  <si>
+    <t>मेरा पहला निष्कर्ष यह था कि वे बेहतर लोग हैं.</t>
+  </si>
+  <si>
+    <t>अब वेब विडियो ने ऐसा कर दिया है कि हम में से कोई भी, या हमारी कोई भी रचनात्मक चीज़ बहुत ही मशहूर हो सकती है, हमारी दुनिया की संस्कृति का हिस्सा हो सकती है।</t>
+  </si>
+  <si>
+    <t>और इस “क्यों” का हेतु “लाभ कमाना” नहीं है. वह तो परिणाम है . यह सदा परिणाम है</t>
+  </si>
+  <si>
+    <t>लक्ष्य यह नहीं कि ज़रूरतमंद लोगों को वह बेचा जाए जो आपके पास है; लक्ष्य वे लोग हैं जिनके विश्वास और आपके विश्वास समान हैं.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">आपको गिनती नही आती अच्छी तरहसे है </t>
+  </si>
+  <si>
+    <t>तो इस कहानी में डेविड कम क्षमता का व्यक्ति है</t>
+  </si>
+  <si>
+    <t xml:space="preserve">तुम यही चाहते थे </t>
+  </si>
+  <si>
+    <t xml:space="preserve">तुम ने मुझे पहचाना नहीं है </t>
   </si>
 </sst>
 </file>
@@ -415,8 +478,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,6 +498,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -721,8 +791,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="8.7265625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +808,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -754,7 +827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>372</v>
       </c>
@@ -767,8 +840,11 @@
       <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>120</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -780,7 +856,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>491</v>
       </c>
@@ -793,8 +869,11 @@
       <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>121</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -806,7 +885,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>731</v>
       </c>
@@ -819,8 +898,11 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>122</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -832,7 +914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>909</v>
       </c>
@@ -845,8 +927,11 @@
       <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>123</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -858,7 +943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1283</v>
       </c>
@@ -871,8 +956,11 @@
       <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>124</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
@@ -884,7 +972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1541</v>
       </c>
@@ -897,8 +985,11 @@
       <c r="D7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>125</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
@@ -910,7 +1001,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1018</v>
       </c>
@@ -923,8 +1014,11 @@
       <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>126</v>
       </c>
       <c r="G8" t="s">
         <v>44</v>
@@ -936,7 +1030,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1085</v>
       </c>
@@ -949,8 +1043,11 @@
       <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>127</v>
       </c>
       <c r="G9" t="s">
         <v>50</v>
@@ -962,7 +1059,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1098</v>
       </c>
@@ -975,8 +1072,11 @@
       <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>128</v>
       </c>
       <c r="G10" t="s">
         <v>55</v>
@@ -988,7 +1088,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1190</v>
       </c>
@@ -1001,8 +1101,11 @@
       <c r="D11" t="s">
         <v>58</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>129</v>
       </c>
       <c r="G11" t="s">
         <v>60</v>
@@ -1014,7 +1117,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1317</v>
       </c>
@@ -1027,8 +1130,11 @@
       <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>130</v>
       </c>
       <c r="G12" t="s">
         <v>66</v>
@@ -1040,7 +1146,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>17192</v>
       </c>
@@ -1053,8 +1159,11 @@
       <c r="D13" t="s">
         <v>69</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>131</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -1066,7 +1175,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>81</v>
       </c>
@@ -1079,8 +1188,11 @@
       <c r="D14" t="s">
         <v>74</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>132</v>
       </c>
       <c r="G14" t="s">
         <v>76</v>
@@ -1092,7 +1204,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="116" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>630</v>
       </c>
@@ -1105,8 +1217,11 @@
       <c r="D15" t="s">
         <v>80</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>133</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -1118,7 +1233,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>724</v>
       </c>
@@ -1131,8 +1246,11 @@
       <c r="D16" t="s">
         <v>84</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>85</v>
+      </c>
+      <c r="F16" t="s">
+        <v>134</v>
       </c>
       <c r="G16" t="s">
         <v>86</v>
@@ -1144,7 +1262,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1064</v>
       </c>
@@ -1157,8 +1275,11 @@
       <c r="D17" t="s">
         <v>89</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>135</v>
       </c>
       <c r="G17" t="s">
         <v>119</v>
@@ -1170,7 +1291,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1117</v>
       </c>
@@ -1183,8 +1304,11 @@
       <c r="D18" t="s">
         <v>93</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>136</v>
       </c>
       <c r="G18" t="s">
         <v>95</v>
@@ -1196,7 +1320,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="87" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1243</v>
       </c>
@@ -1209,8 +1333,11 @@
       <c r="D19" t="s">
         <v>98</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>99</v>
+      </c>
+      <c r="F19" t="s">
+        <v>137</v>
       </c>
       <c r="G19" t="s">
         <v>100</v>
@@ -1222,7 +1349,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="116" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2560</v>
       </c>
@@ -1235,8 +1362,11 @@
       <c r="D20" t="s">
         <v>104</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>105</v>
+      </c>
+      <c r="F20" t="s">
+        <v>138</v>
       </c>
       <c r="G20" t="s">
         <v>106</v>
@@ -1248,7 +1378,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>392111</v>
       </c>
@@ -1261,8 +1391,11 @@
       <c r="D21" t="s">
         <v>109</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>110</v>
+      </c>
+      <c r="F21" t="s">
+        <v>139</v>
       </c>
       <c r="G21" t="s">
         <v>111</v>
@@ -1274,7 +1407,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2288136</v>
       </c>
@@ -1287,8 +1420,11 @@
       <c r="D22" t="s">
         <v>114</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>140</v>
       </c>
       <c r="G22" t="s">
         <v>116</v>

--- a/Hindi 24 sentences.xlsx
+++ b/Hindi 24 sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba77bf8d4b5edec/Desktop/IIITH DOCUMENTS/prosody_questionnaire/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F03BCFB-37AF-48DB-9CD1-1CA3791C23E3}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C419E43-68ED-4615-8472-FFD69EB7ED17}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="136">
   <si>
     <t>sample id</t>
   </si>
@@ -118,51 +118,9 @@
     <t>QijH4UAqGD8_sentence_00909.m4a</t>
   </si>
   <si>
-    <t>v21</t>
-  </si>
-  <si>
-    <t>But that's all it was.</t>
-  </si>
-  <si>
-    <t>पर यही सब था​.</t>
-  </si>
-  <si>
-    <t>लेकिन यह सब था.</t>
-  </si>
-  <si>
-    <t>eaCrsBtiYA4_sentence_01283.m4a</t>
-  </si>
-  <si>
-    <t>It's all in English."</t>
-  </si>
-  <si>
-    <t>वो तो पूरा ही अंग्रेजी में है।"</t>
-  </si>
-  <si>
-    <t>यह सब अंग्रेजी में है".</t>
-  </si>
-  <si>
-    <t>tFX68SJs2-0_sentence_01541.m4a</t>
-  </si>
-  <si>
-    <t>Where do we even begin with that insight?</t>
-  </si>
-  <si>
-    <t>इस समझ की शुरुआत भी कहाँ से करें?</t>
-  </si>
-  <si>
-    <t>हम उस अंतर्दृष्टि से कहाँ से शुरू करें?</t>
-  </si>
-  <si>
-    <t>even</t>
-  </si>
-  <si>
     <t>भी</t>
   </si>
   <si>
-    <t>MB5IX-np5fE_sentence_01018.m4a</t>
-  </si>
-  <si>
     <t>We just happen to make great computers.</t>
   </si>
   <si>
@@ -178,21 +136,6 @@
     <t>qp0HIF3SfI4_sentence_01085.m4a</t>
   </si>
   <si>
-    <t>I also thought, isn't this kind of obvious?</t>
-  </si>
-  <si>
-    <t>मैंने यह भी सोचा, क्या यह स्पष्ट नहीं है?</t>
-  </si>
-  <si>
-    <t>मैंने सोचा, क्या यह स्पष्ट नहीं है?</t>
-  </si>
-  <si>
-    <t>also</t>
-  </si>
-  <si>
-    <t>MB5IX-np5fE_sentence_01098.m4a</t>
-  </si>
-  <si>
     <t>In fact, some of his ideas were bad.</t>
   </si>
   <si>
@@ -271,21 +214,6 @@
     <t>lmyZMtPVodo_sentence_00630.m4a</t>
   </si>
   <si>
-    <t>But now Web video has made it so that any of us or any of the creative things that we do can become completely famous in a part of our world's culture.</t>
-  </si>
-  <si>
-    <t>अब तो वेब विडियो ने ऐसा कर दिया है कि हम में से कोई भी, या हमारी कोई भी रचनात्मक चीज़ बहुत ही मशहूर हो सकती है, हमारी दुनिया की संस्कृति का हिस्सा हो सकती है।</t>
-  </si>
-  <si>
-    <t>लेकिन अब वेब वीडियो ने इसे ऐसा बना दिया है कि हममें से कोई भी या जो भी रचनात्मक काम हम करते हैं वह पूरी तरह से हमारे विश्व की संस्कृति के एक हिस्से में प्रसिद्ध हो सकता है।</t>
-  </si>
-  <si>
-    <t>now</t>
-  </si>
-  <si>
-    <t>BpxVIwCbBK0_sentence_00724.m4a</t>
-  </si>
-  <si>
     <t>And by "why" I don't mean "to make a profit." That's a result. It's always a result.</t>
   </si>
   <si>
@@ -331,21 +259,6 @@
     <t>RcGyVTAoXEU_sentence_01243.m4a</t>
   </si>
   <si>
-    <t>So David, in that story, is supposed to be the underdog, right?</t>
-  </si>
-  <si>
-    <t>तो इस कहानी में डेविड कम क्षमता का व्यक्ति है,है ना?</t>
-  </si>
-  <si>
-    <t>तो डेविड, उस कहानी में, है कि underdog होना चाहिए, सही है?</t>
-  </si>
-  <si>
-    <t>right?</t>
-  </si>
-  <si>
-    <t>ziGD7vQOwl8_sentence_02560.m4a</t>
-  </si>
-  <si>
     <t>Is this what you wanted?</t>
   </si>
   <si>
@@ -394,21 +307,9 @@
     <t>सभी का कल्याण करना, यह तो समुदाय का काम है।</t>
   </si>
   <si>
-    <t>पर यह सब था​.</t>
-  </si>
-  <si>
-    <t>वो तो पूरा अंग्रेजी में है।"</t>
-  </si>
-  <si>
-    <t>इस समझ की शुरुआत कहाँ से करें?</t>
-  </si>
-  <si>
     <t>हम बढ़िया कंप्यूटर बनाते हैं.</t>
   </si>
   <si>
-    <t>मैंने यह सोचा, क्या यह स्पष्ट नहीं है?</t>
-  </si>
-  <si>
     <t>वास्तव में उनके कुछ विचार गलत थे.</t>
   </si>
   <si>
@@ -424,9 +325,6 @@
     <t>मेरा पहला निष्कर्ष यह था कि वे बेहतर लोग हैं.</t>
   </si>
   <si>
-    <t>अब वेब विडियो ने ऐसा कर दिया है कि हम में से कोई भी, या हमारी कोई भी रचनात्मक चीज़ बहुत ही मशहूर हो सकती है, हमारी दुनिया की संस्कृति का हिस्सा हो सकती है।</t>
-  </si>
-  <si>
     <t>और इस “क्यों” का हेतु “लाभ कमाना” नहीं है. वह तो परिणाम है . यह सदा परिणाम है</t>
   </si>
   <si>
@@ -436,13 +334,100 @@
     <t xml:space="preserve">आपको गिनती नही आती अच्छी तरहसे है </t>
   </si>
   <si>
-    <t>तो इस कहानी में डेविड कम क्षमता का व्यक्ति है</t>
-  </si>
-  <si>
     <t xml:space="preserve">तुम यही चाहते थे </t>
   </si>
   <si>
     <t xml:space="preserve">तुम ने मुझे पहचाना नहीं है </t>
+  </si>
+  <si>
+    <t>I find foreign languages very interesting.</t>
+  </si>
+  <si>
+    <t>very</t>
+  </si>
+  <si>
+    <t>मेरे ख़याल से विदेशी भाषाएँ बहुत ही दिलचस्प होतीं हैं।</t>
+  </si>
+  <si>
+    <t>मेरे ख़याल से विदेशी भाषाएँ बहुत दिलचस्प होतीं हैं।</t>
+  </si>
+  <si>
+    <t>That child is only four, but he can already count to 100.</t>
+  </si>
+  <si>
+    <t>वह बच्चा हालांकि केवल चार साल का ही है, वह अभी से ही सौ तक गिनती कर सकता है।</t>
+  </si>
+  <si>
+    <t>वह बच्चा हालांकि केवल चार साल का है, वह अभी से ही सौ तक गिनती कर सकता है।</t>
+  </si>
+  <si>
+    <t>only four</t>
+  </si>
+  <si>
+    <t>वह बच्चा केवल चार साल का है, लेकिन वह पहले से ही 100 तक गिन सकता है।</t>
+  </si>
+  <si>
+    <t>Don't drink any alcohol.</t>
+  </si>
+  <si>
+    <t>शराब की एक बूंद भी मत पियो।</t>
+  </si>
+  <si>
+    <t>शराब की एक बूंद मत पियो।</t>
+  </si>
+  <si>
+    <t>शराब का सेवन बिल्कुल न करें।</t>
+  </si>
+  <si>
+    <t>any alcohol</t>
+  </si>
+  <si>
+    <t>There weren't any children in the park yesterday.</t>
+  </si>
+  <si>
+    <t>कल पार्क में एक भी बच्चा नहीं था।</t>
+  </si>
+  <si>
+    <t>कल पार्क में एक बच्चा नहीं था।</t>
+  </si>
+  <si>
+    <t>कल पार्क में कोई बच्चा नहीं था।</t>
+  </si>
+  <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>क्या आप यही चाहते थे?</t>
+  </si>
+  <si>
+    <t>Tom won't do that even if you ask him.</t>
+  </si>
+  <si>
+    <t>यदि तुम उसे पूछो तो भी टॉम उसे नहीं करेगा।</t>
+  </si>
+  <si>
+    <t>यदि तुम उसे पूछो भी टॉम उसे नहीं करेगा।</t>
+  </si>
+  <si>
+    <t>टॉम ऐसा नहीं करेगा, भले ही आप उससे पूछें।</t>
+  </si>
+  <si>
+    <t>even if</t>
+  </si>
+  <si>
+    <t>1801.mp3</t>
+  </si>
+  <si>
+    <t>47510.mp3</t>
+  </si>
+  <si>
+    <t>67306.mp3</t>
+  </si>
+  <si>
+    <t>244589.mp3</t>
+  </si>
+  <si>
+    <t>9419078.mp3</t>
   </si>
 </sst>
 </file>
@@ -478,11 +463,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -873,7 +859,7 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -902,7 +888,7 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -931,7 +917,7 @@
         <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -943,91 +929,91 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1283</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="F6" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1541</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1018</v>
       </c>
       <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="87" x14ac:dyDescent="0.35">
@@ -1038,25 +1024,25 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -1064,28 +1050,28 @@
         <v>1098</v>
       </c>
       <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -1096,25 +1082,25 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -1122,28 +1108,28 @@
         <v>1317</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -1151,28 +1137,28 @@
         <v>17192</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="203" x14ac:dyDescent="0.35">
@@ -1183,25 +1169,25 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="116" x14ac:dyDescent="0.35">
@@ -1212,54 +1198,54 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>724</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>83</v>
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="F16" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
@@ -1270,25 +1256,25 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
         <v>90</v>
       </c>
-      <c r="F17" t="s">
-        <v>135</v>
-      </c>
-      <c r="G17" t="s">
-        <v>119</v>
-      </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I17" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="246.5" x14ac:dyDescent="0.35">
@@ -1299,25 +1285,25 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="87" x14ac:dyDescent="0.35">
@@ -1328,54 +1314,54 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="116" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2560</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" t="s">
-        <v>138</v>
-      </c>
       <c r="G20" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="58" x14ac:dyDescent="0.35">
@@ -1383,28 +1369,28 @@
         <v>392111</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
@@ -1412,28 +1398,28 @@
         <v>2288136</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Hindi 24 sentences.xlsx
+++ b/Hindi 24 sentences.xlsx
@@ -463,12 +463,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -936,7 +935,7 @@
       <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>106</v>
       </c>
       <c r="D6" t="s">
@@ -958,14 +957,14 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1541</v>
       </c>
       <c r="B7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>110</v>
       </c>
       <c r="D7" t="s">
@@ -987,14 +986,14 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1018</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
@@ -1052,7 +1051,7 @@
       <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>120</v>
       </c>
       <c r="D10" t="s">
@@ -1219,14 +1218,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>724</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>126</v>
       </c>
       <c r="D16" t="s">
@@ -1335,14 +1334,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2560</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>79</v>
       </c>
       <c r="D20" t="s">

--- a/Hindi 24 sentences.xlsx
+++ b/Hindi 24 sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba77bf8d4b5edec/Desktop/IIITH DOCUMENTS/prosody_questionnaire/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C419E43-68ED-4615-8472-FFD69EB7ED17}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{44433301-E5AE-42B2-AC9E-2D20BA14D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D26CFC70-22C6-4717-A6DF-657B05B37532}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="140">
   <si>
     <t>sample id</t>
   </si>
@@ -397,9 +397,6 @@
     <t>any</t>
   </si>
   <si>
-    <t>क्या आप यही चाहते थे?</t>
-  </si>
-  <si>
     <t>Tom won't do that even if you ask him.</t>
   </si>
   <si>
@@ -428,6 +425,21 @@
   </si>
   <si>
     <t>9419078.mp3</t>
+  </si>
+  <si>
+    <t>It's nice, isn't it?</t>
+  </si>
+  <si>
+    <t>अच्छा है, है ना?</t>
+  </si>
+  <si>
+    <t>अच्छा है</t>
+  </si>
+  <si>
+    <t>यह अच्छा है, नहीं?</t>
+  </si>
+  <si>
+    <t>2548180.mp3</t>
   </si>
 </sst>
 </file>
@@ -954,7 +966,7 @@
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
@@ -983,7 +995,7 @@
         <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -1012,7 +1024,7 @@
         <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="87" x14ac:dyDescent="0.35">
@@ -1070,7 +1082,7 @@
         <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -1226,25 +1238,25 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" t="s">
         <v>126</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="G16" t="s">
         <v>129</v>
-      </c>
-      <c r="F16" t="s">
-        <v>128</v>
-      </c>
-      <c r="G16" t="s">
-        <v>130</v>
       </c>
       <c r="H16" t="s">
         <v>58</v>
       </c>
       <c r="I16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
@@ -1334,7 +1346,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2560</v>
       </c>
@@ -1342,16 +1354,16 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="G20" t="s">
         <v>82</v>
@@ -1360,7 +1372,7 @@
         <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="58" x14ac:dyDescent="0.35">
